--- a/output/pdf_financials_xlsx/TNZ.xlsx
+++ b/output/pdf_financials_xlsx/TNZ.xlsx
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.294885</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.245299</v>
@@ -2190,13 +2190,13 @@
         <v>0.939048</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>2.387</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>4.098</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>7.206</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.082465</v>
+        <v>0.21242</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.33914</v>
@@ -2256,13 +2256,13 @@
         <v>4.375239</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.145874</v>
+        <v>-1.758874</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.249</v>
+        <v>2.849</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.249</v>
+        <v>5.957</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-5.773182163446897</v>
+        <v>14.87102837760735</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>30.50662368117817</v>
@@ -2322,13 +2322,13 @@
         <v>73.90310556823992</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-76.84659870250232</v>
+        <v>-32.60192771084338</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-15.7284976703186</v>
+        <v>35.87709356504219</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-7.605650956034587</v>
+        <v>36.27450980392157</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -6081,10 +6081,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.294885</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.245299</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6093,37 +6093,37 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.939048</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.387</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>4.098</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>7.206</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>6.906</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>6.433</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>19.962</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>20.871</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>111.598</v>
       </c>
     </row>
     <row r="101">
@@ -7032,34 +7032,34 @@
         <v>-4.857036</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.061</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-6.713</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-6.414</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.167</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.519</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.948</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-50.184</v>
       </c>
     </row>
     <row r="119">
@@ -42472,7 +42472,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -43530,7 +43530,11 @@
           <t>Exploration and evaluation asset expenditures 11</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -45664,7 +45668,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -46279,7 +46283,11 @@
           <t>Exploration and evaluation asset expenditures 9</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -50833,7 +50841,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -52089,7 +52097,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -53060,7 +53072,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -56672,7 +56684,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -63607,7 +63619,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E620" s="5" t="n">
@@ -65417,7 +65429,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -67684,7 +67696,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -70491,7 +70503,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -75950,7 +75962,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E757" s="5" t="n">

--- a/output/pdf_financials_xlsx/TNZ.xlsx
+++ b/output/pdf_financials_xlsx/TNZ.xlsx
@@ -1090,19 +1090,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.026401</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020861</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -2118,19 +2118,19 @@
         <v>-1.570611</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.628834</v>
+        <v>-0.655235</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.436191</v>
+        <v>3.41533</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.145874</v>
+        <v>-4.199874</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.249</v>
+        <v>-1.409</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.249</v>
+        <v>-1.267</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2250,19 +2250,19 @@
         <v>-1.320671</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.278789</v>
+        <v>-0.30519</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.375239</v>
+        <v>4.354378</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.758874</v>
+        <v>-1.812874</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.849</v>
+        <v>2.689</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.957</v>
+        <v>5.939</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2316,19 +2316,19 @@
         <v>-140.3250912977832</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-13.69081790149981</v>
+        <v>-14.987322725641</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>73.90310556823992</v>
+        <v>73.55073791809347</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-32.60192771084338</v>
+        <v>-33.60285449490269</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>35.87709356504219</v>
+        <v>33.86223397556983</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>36.27450980392157</v>
+        <v>36.16490074290586</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.961242</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.916415</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.909105</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.18104</v>
@@ -2553,10 +2553,10 @@
         <v>50.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>139.906</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>64.241</v>
       </c>
     </row>
     <row r="35">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.961242</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.916415</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.909105</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.18104</v>
@@ -2661,10 +2661,10 @@
         <v>50.3</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>139.906</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>64.241</v>
       </c>
     </row>
     <row r="37">
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.052369</v>
+        <v>1.091127</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.219404</v>
+        <v>1.302989</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.76217</v>
+        <v>0.853065</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.34186</v>
@@ -3309,10 +3309,10 @@
         <v>34.186</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>182.307</v>
+        <v>42.401</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>135.443</v>
+        <v>71.202</v>
       </c>
     </row>
     <row r="49">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -64620,7 +64620,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -74975,7 +74975,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -76235,7 +76235,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E760" s="5" t="n">

--- a/output/pdf_financials_xlsx/TNZ.xlsx
+++ b/output/pdf_financials_xlsx/TNZ.xlsx
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>0.018371</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.018088</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.016597</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.010375</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.082465</v>
+        <v>-0.100836</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.09384099999999999</v>
+        <v>0.075753</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.570611</v>
+        <v>-1.587208</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.655235</v>
+        <v>-0.66561</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.41533</v>
+        <v>3.35533</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-4.199874</v>
@@ -2241,19 +2241,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.21242</v>
+        <v>0.194049</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.33914</v>
+        <v>0.321052</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.320671</v>
+        <v>-1.337268</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.30519</v>
+        <v>-0.315565</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.354378</v>
+        <v>4.294378</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.812874</v>
@@ -2307,19 +2307,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>14.87102837760735</v>
+        <v>13.58491754847156</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>30.50662368117817</v>
+        <v>28.87955577663978</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-140.3250912977832</v>
+        <v>-142.088570271933</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-14.987322725641</v>
+        <v>-15.49682000038304</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>73.55073791809347</v>
+        <v>72.53726497773654</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-33.60285449490269</v>
@@ -6708,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.065</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>1.213947</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -50012,7 +50012,11 @@
           <t>Issuance of common shares, net of issue costs 15</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -60019,7 +60023,11 @@
           <t>Proceeds from disposal of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E580" t="inlineStr">
         <is>
           <t>-</t>
@@ -62798,7 +62806,11 @@
           <t>Loss on disposal of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
@@ -63073,7 +63085,11 @@
           <t>Proceeds from disposal of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -63894,7 +63910,11 @@
           <t>Loss on disposal of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -64078,7 +64098,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
@@ -73994,7 +74018,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E735" s="5" t="n">
         <v>-0.018371</v>
       </c>
@@ -75157,7 +75185,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E748" t="inlineStr">
         <is>
           <t>-</t>
